--- a/data/trans_orig/P13_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P13_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2007</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258401</t>
+          <t>257764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269654</t>
+          <t>269390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243742</t>
+          <t>244630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257366</t>
+          <t>257028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>506824</t>
+          <t>507820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>524046</t>
+          <t>523978</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14315</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34461</t>
+          <t>34992</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>22958</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45896</t>
+          <t>45047</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>42639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72680</t>
+          <t>71316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>458614</t>
+          <t>458083</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>478760</t>
+          <t>478687</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>458053</t>
+          <t>458902</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480714</t>
+          <t>480991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>924344</t>
+          <t>925708</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>953983</t>
+          <t>954385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307371</t>
+          <t>307816</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317890</t>
+          <t>317888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>320612</t>
+          <t>320780</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332389</t>
+          <t>332370</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632927</t>
+          <t>633943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>648703</t>
+          <t>649074</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16235</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22785</t>
+          <t>22892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>346445</t>
+          <t>347179</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357571</t>
+          <t>357585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>355221</t>
+          <t>354768</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366717</t>
+          <t>367394</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707342</t>
+          <t>707235</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>722355</t>
+          <t>722527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10925</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>22840</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28307</t>
+          <t>28226</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192383</t>
+          <t>192199</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201469</t>
+          <t>201481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>185027</t>
+          <t>184828</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199618</t>
+          <t>200360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>382669</t>
+          <t>382750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>399357</t>
+          <t>398948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270811</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266384</t>
+          <t>267239</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276078</t>
+          <t>276163</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>537806</t>
+          <t>537190</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>546986</t>
+          <t>546969</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40851</t>
+          <t>39151</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29700</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55335</t>
+          <t>56060</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53831</t>
+          <t>53380</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85318</t>
+          <t>86876</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>574176</t>
+          <t>575876</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>596630</t>
+          <t>597020</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>582884</t>
+          <t>582159</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>608519</t>
+          <t>608077</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1167928</t>
+          <t>1166370</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1199415</t>
+          <t>1199866</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23632</t>
+          <t>22939</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47606</t>
+          <t>45541</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33123</t>
+          <t>32987</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60683</t>
+          <t>59867</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63460</t>
+          <t>61268</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99778</t>
+          <t>97134</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>696189</t>
+          <t>698254</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>720163</t>
+          <t>720856</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>722828</t>
+          <t>723644</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>750388</t>
+          <t>750524</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1427528</t>
+          <t>1430172</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1463846</t>
+          <t>1466038</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>85961</t>
+          <t>86111</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>125506</t>
+          <t>127563</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>137011</t>
+          <t>140887</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>189635</t>
+          <t>192328</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>238296</t>
+          <t>237495</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>303755</t>
+          <t>301003</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3151037</t>
+          <t>3148980</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3190582</t>
+          <t>3190432</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3189562</t>
+          <t>3186869</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3242186</t>
+          <t>3238310</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6351986</t>
+          <t>6354738</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6417445</t>
+          <t>6418246</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2012</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23406</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39930</t>
+          <t>40289</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68228</t>
+          <t>69504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53738</t>
+          <t>52807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84055</t>
+          <t>85080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271332</t>
+          <t>272313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285723</t>
+          <t>286361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>219017</t>
+          <t>217741</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247315</t>
+          <t>246956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>497928</t>
+          <t>496903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>528245</t>
+          <t>529176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35684</t>
+          <t>35438</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43517</t>
+          <t>43963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73251</t>
+          <t>73534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62455</t>
+          <t>64822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98541</t>
+          <t>100429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468896</t>
+          <t>469142</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490672</t>
+          <t>490013</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450514</t>
+          <t>450231</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480248</t>
+          <t>479802</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>929804</t>
+          <t>927916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>965890</t>
+          <t>963523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17780</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>32874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21401</t>
+          <t>21317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45702</t>
+          <t>43940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306266</t>
+          <t>306390</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320039</t>
+          <t>320103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308940</t>
+          <t>308146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326682</t>
+          <t>327168</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>619364</t>
+          <t>621126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643665</t>
+          <t>643749</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16836</t>
+          <t>17386</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>25650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47069</t>
+          <t>48257</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33563</t>
+          <t>33875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59131</t>
+          <t>58782</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356181</t>
+          <t>355631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368649</t>
+          <t>367868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339928</t>
+          <t>338740</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362367</t>
+          <t>361347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700882</t>
+          <t>701231</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>726450</t>
+          <t>726138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>12943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>17099</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37215</t>
+          <t>36408</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>21587</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>44443</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198765</t>
+          <t>199675</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210229</t>
+          <t>210421</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182376</t>
+          <t>183183</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202956</t>
+          <t>202492</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>388757</t>
+          <t>387766</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>410005</t>
+          <t>410622</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20399</t>
+          <t>20962</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26984</t>
+          <t>27416</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20246</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42074</t>
+          <t>41606</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253582</t>
+          <t>253019</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266972</t>
+          <t>267688</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253047</t>
+          <t>252615</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269687</t>
+          <t>268773</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>511938</t>
+          <t>512406</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533766</t>
+          <t>533661</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>25022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26009</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53216</t>
+          <t>52528</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36946</t>
+          <t>37825</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68317</t>
+          <t>69471</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>636685</t>
+          <t>637766</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654770</t>
+          <t>653899</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>639539</t>
+          <t>640227</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>666746</t>
+          <t>667220</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1287226</t>
+          <t>1286072</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1318597</t>
+          <t>1317718</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54604</t>
+          <t>53993</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87443</t>
+          <t>88604</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68352</t>
+          <t>67446</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>104929</t>
+          <t>101938</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>131093</t>
+          <t>130126</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>180974</t>
+          <t>179523</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>690625</t>
+          <t>689464</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>723464</t>
+          <t>724075</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>718924</t>
+          <t>721915</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>755501</t>
+          <t>756407</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1420947</t>
+          <t>1422398</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1470828</t>
+          <t>1471795</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>135106</t>
+          <t>134333</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>188271</t>
+          <t>185836</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>296176</t>
+          <t>297009</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>369679</t>
+          <t>369396</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>444062</t>
+          <t>448149</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>535778</t>
+          <t>534402</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3235565</t>
+          <t>3238000</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3288730</t>
+          <t>3289503</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3185578</t>
+          <t>3185861</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3259081</t>
+          <t>3258248</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6443315</t>
+          <t>6444691</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6535031</t>
+          <t>6530944</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2016</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2016 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9395</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26562</t>
+          <t>26216</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19856</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40010</t>
+          <t>40639</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33660</t>
+          <t>33209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59316</t>
+          <t>59988</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267199</t>
+          <t>267545</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284153</t>
+          <t>284366</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248693</t>
+          <t>248064</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268847</t>
+          <t>269482</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>523148</t>
+          <t>522476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>548804</t>
+          <t>549255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22015</t>
+          <t>20296</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>11410</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>29705</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>20943</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45292</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480560</t>
+          <t>482279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496488</t>
+          <t>496517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>493651</t>
+          <t>493379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512519</t>
+          <t>511674</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>980367</t>
+          <t>982640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1004413</t>
+          <t>1004716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308880</t>
+          <t>308258</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316926</t>
+          <t>316991</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327997</t>
+          <t>328442</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640328</t>
+          <t>640828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651290</t>
+          <t>651143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26314</t>
+          <t>26315</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17753</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38349</t>
+          <t>38865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32575</t>
+          <t>32463</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59609</t>
+          <t>58537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342677</t>
+          <t>342676</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358887</t>
+          <t>358989</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348934</t>
+          <t>348418</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369530</t>
+          <t>369617</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696665</t>
+          <t>697737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>723699</t>
+          <t>723811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9329</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25023</t>
+          <t>25090</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15618</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34296</t>
+          <t>35078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196744</t>
+          <t>197058</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208134</t>
+          <t>207330</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192677</t>
+          <t>192610</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208371</t>
+          <t>208599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>394625</t>
+          <t>393843</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>413303</t>
+          <t>413051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33250</t>
+          <t>32173</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21255</t>
+          <t>22457</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44800</t>
+          <t>46884</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245331</t>
+          <t>245303</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257248</t>
+          <t>257750</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239865</t>
+          <t>240942</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259772</t>
+          <t>259530</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>491438</t>
+          <t>489354</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>514983</t>
+          <t>513781</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17551</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39344</t>
+          <t>39389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38232</t>
+          <t>37667</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67325</t>
+          <t>66956</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62128</t>
+          <t>62756</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98076</t>
+          <t>97296</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>617214</t>
+          <t>617169</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>639007</t>
+          <t>638893</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>622698</t>
+          <t>623067</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>651791</t>
+          <t>652356</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1248505</t>
+          <t>1249285</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1284453</t>
+          <t>1283825</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14308</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33013</t>
+          <t>33792</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>19373</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43953</t>
+          <t>43966</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38282</t>
+          <t>38305</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69324</t>
+          <t>68130</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>745570</t>
+          <t>744791</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>764275</t>
+          <t>764711</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>780179</t>
+          <t>780166</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>804821</t>
+          <t>804759</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1533391</t>
+          <t>1534585</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1564433</t>
+          <t>1564410</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>97926</t>
+          <t>96531</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>140090</t>
+          <t>140779</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>167866</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>223954</t>
+          <t>226190</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>280753</t>
+          <t>279351</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>353544</t>
+          <t>353703</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3253288</t>
+          <t>3252599</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3295452</t>
+          <t>3296847</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3315550</t>
+          <t>3313314</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3371638</t>
+          <t>3369504</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6579337</t>
+          <t>6579178</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6652128</t>
+          <t>6653530</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2023</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11649</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300407</t>
+          <t>299794</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309892</t>
+          <t>309561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282057</t>
+          <t>282489</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288282</t>
+          <t>288606</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>585775</t>
+          <t>586431</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>596934</t>
+          <t>597097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34100</t>
+          <t>34265</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29169</t>
+          <t>29787</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51251</t>
+          <t>50228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47532</t>
+          <t>46929</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76329</t>
+          <t>75919</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483419</t>
+          <t>483254</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503781</t>
+          <t>504346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463718</t>
+          <t>464741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485800</t>
+          <t>485182</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>956159</t>
+          <t>956569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>984956</t>
+          <t>985559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16985</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33560</t>
+          <t>33697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29152</t>
+          <t>29543</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46795</t>
+          <t>46991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49408</t>
+          <t>50117</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73206</t>
+          <t>75231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281486</t>
+          <t>281349</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>298061</t>
+          <t>298218</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>302333</t>
+          <t>302137</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319976</t>
+          <t>319585</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>590967</t>
+          <t>588942</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>614765</t>
+          <t>614056</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>11758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30771</t>
+          <t>29983</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>15095</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36378</t>
+          <t>36552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>32341</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59893</t>
+          <t>61047</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>281786</t>
+          <t>282574</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300879</t>
+          <t>300799</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>435892</t>
+          <t>435718</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>456926</t>
+          <t>457175</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>724933</t>
+          <t>723779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752771</t>
+          <t>752485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>14636</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13304</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>166099</t>
+          <t>165474</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174053</t>
+          <t>173991</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193754</t>
+          <t>193608</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201500</t>
+          <t>201299</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>362683</t>
+          <t>362649</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>373682</t>
+          <t>374066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21510</t>
+          <t>20476</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>17815</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29564</t>
+          <t>29866</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>29636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46575</t>
+          <t>45834</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248126</t>
+          <t>249160</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259667</t>
+          <t>260260</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>227492</t>
+          <t>227190</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>239384</t>
+          <t>239241</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>480117</t>
+          <t>480858</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>497150</t>
+          <t>497056</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56077</t>
+          <t>55379</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28451</t>
+          <t>28067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81715</t>
+          <t>82136</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63993</t>
+          <t>65634</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>124180</t>
+          <t>123215</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>567173</t>
+          <t>567871</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>592868</t>
+          <t>592815</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>767550</t>
+          <t>767129</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>820814</t>
+          <t>821198</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1348334</t>
+          <t>1349299</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1408521</t>
+          <t>1406880</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14559</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51953</t>
+          <t>53874</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42506</t>
+          <t>42368</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63065</t>
+          <t>64239</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52636</t>
+          <t>54716</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>109120</t>
+          <t>110011</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>876147</t>
+          <t>874226</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>913541</t>
+          <t>911921</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>653957</t>
+          <t>652783</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>674516</t>
+          <t>674654</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1536002</t>
+          <t>1535111</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1592486</t>
+          <t>1590406</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>124843</t>
+          <t>130009</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>196052</t>
+          <t>196862</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>202910</t>
+          <t>203776</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>280723</t>
+          <t>280250</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>365723</t>
+          <t>361230</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>459618</t>
+          <t>459412</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3260240</t>
+          <t>3259430</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3331449</t>
+          <t>3326283</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3376864</t>
+          <t>3377337</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3454677</t>
+          <t>3453811</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6654261</t>
+          <t>6654467</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6748156</t>
+          <t>6752649</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P13_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15246</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16208</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26028</t>
+          <t>25484</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257764</t>
+          <t>258069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269390</t>
+          <t>269658</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>244630</t>
+          <t>244261</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257028</t>
+          <t>256699</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>507820</t>
+          <t>508364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>523978</t>
+          <t>524214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34992</t>
+          <t>33852</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22958</t>
+          <t>23562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45047</t>
+          <t>45086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42639</t>
+          <t>42170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71316</t>
+          <t>71721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>458083</t>
+          <t>459223</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>478687</t>
+          <t>478958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>458902</t>
+          <t>458863</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480991</t>
+          <t>480387</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>925708</t>
+          <t>925303</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>954385</t>
+          <t>954854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14632</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20315</t>
+          <t>19868</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307816</t>
+          <t>308103</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317888</t>
+          <t>317894</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>320780</t>
+          <t>321566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332370</t>
+          <t>332391</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>633943</t>
+          <t>634390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>649074</t>
+          <t>648994</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>16482</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22892</t>
+          <t>22384</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347179</t>
+          <t>347889</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357585</t>
+          <t>357692</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>354768</t>
+          <t>354974</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367394</t>
+          <t>367349</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707235</t>
+          <t>707743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>722527</t>
+          <t>722329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22840</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28226</t>
+          <t>28105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192199</t>
+          <t>192223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201481</t>
+          <t>201500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184828</t>
+          <t>184796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200360</t>
+          <t>199898</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>382750</t>
+          <t>382871</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>398948</t>
+          <t>398535</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267239</t>
+          <t>266039</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276163</t>
+          <t>276165</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>537190</t>
+          <t>537230</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>546969</t>
+          <t>546924</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18007</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39151</t>
+          <t>38907</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30142</t>
+          <t>29520</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56060</t>
+          <t>55143</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53380</t>
+          <t>54601</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86876</t>
+          <t>86046</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>575876</t>
+          <t>576120</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597020</t>
+          <t>597082</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>582159</t>
+          <t>583076</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>608077</t>
+          <t>608699</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1166370</t>
+          <t>1167200</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1199866</t>
+          <t>1198645</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22939</t>
+          <t>23167</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45541</t>
+          <t>45776</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32987</t>
+          <t>34132</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59867</t>
+          <t>62066</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61268</t>
+          <t>63133</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97134</t>
+          <t>97630</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>698254</t>
+          <t>698019</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>720856</t>
+          <t>720628</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>723644</t>
+          <t>721445</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>750524</t>
+          <t>749379</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1430172</t>
+          <t>1429676</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1466038</t>
+          <t>1464173</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>86111</t>
+          <t>84933</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>127563</t>
+          <t>127475</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>140887</t>
+          <t>140324</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>192328</t>
+          <t>190043</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>237495</t>
+          <t>235509</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>301003</t>
+          <t>302413</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3148980</t>
+          <t>3149068</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3190432</t>
+          <t>3191610</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3186869</t>
+          <t>3189154</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3238310</t>
+          <t>3238873</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6354738</t>
+          <t>6353328</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6418246</t>
+          <t>6420232</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22425</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40289</t>
+          <t>39849</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69504</t>
+          <t>66944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52807</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85080</t>
+          <t>85813</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>272313</t>
+          <t>270646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286361</t>
+          <t>285332</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>217741</t>
+          <t>220301</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246956</t>
+          <t>247396</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>496903</t>
+          <t>496170</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>529176</t>
+          <t>528175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,75%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14567</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35438</t>
+          <t>35112</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43963</t>
+          <t>42582</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73534</t>
+          <t>73579</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64822</t>
+          <t>63141</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100429</t>
+          <t>100210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>469142</t>
+          <t>469468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490013</t>
+          <t>491223</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450231</t>
+          <t>450186</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479802</t>
+          <t>481183</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>927916</t>
+          <t>928135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>963523</t>
+          <t>965204</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17656</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32874</t>
+          <t>32467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21317</t>
+          <t>20408</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43940</t>
+          <t>41896</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306390</t>
+          <t>305830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320103</t>
+          <t>320061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308146</t>
+          <t>308553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327168</t>
+          <t>326797</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>621126</t>
+          <t>623170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643749</t>
+          <t>644658</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17386</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25650</t>
+          <t>25942</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48257</t>
+          <t>48218</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33875</t>
+          <t>33231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58782</t>
+          <t>58766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>355631</t>
+          <t>356237</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367868</t>
+          <t>368857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>338740</t>
+          <t>338779</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361347</t>
+          <t>361055</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>701231</t>
+          <t>701247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>726138</t>
+          <t>726782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>12724</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17099</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36408</t>
+          <t>35629</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21587</t>
+          <t>21099</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44443</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199675</t>
+          <t>199894</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210421</t>
+          <t>210469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183183</t>
+          <t>183962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202492</t>
+          <t>203030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>387766</t>
+          <t>388771</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>410622</t>
+          <t>411110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20962</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27416</t>
+          <t>27086</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>20427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>41489</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253019</t>
+          <t>253620</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267688</t>
+          <t>267659</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>252615</t>
+          <t>252945</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268773</t>
+          <t>268794</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>512406</t>
+          <t>512523</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533661</t>
+          <t>533585</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>8250</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25022</t>
+          <t>25412</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>25222</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52528</t>
+          <t>52341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37825</t>
+          <t>36485</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69471</t>
+          <t>67495</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>637766</t>
+          <t>637376</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>653899</t>
+          <t>654538</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>640227</t>
+          <t>640414</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>667220</t>
+          <t>667533</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1286072</t>
+          <t>1288048</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1317718</t>
+          <t>1319058</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53993</t>
+          <t>53730</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88604</t>
+          <t>88253</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67446</t>
+          <t>66434</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101938</t>
+          <t>102953</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130126</t>
+          <t>129930</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>179523</t>
+          <t>179433</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>689464</t>
+          <t>689815</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>724075</t>
+          <t>724338</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>721915</t>
+          <t>720900</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>756407</t>
+          <t>757419</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1422398</t>
+          <t>1422488</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1471795</t>
+          <t>1471991</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>134333</t>
+          <t>135453</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>185836</t>
+          <t>190759</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>297009</t>
+          <t>299047</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>369396</t>
+          <t>365052</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>448149</t>
+          <t>443214</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>534402</t>
+          <t>537191</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3238000</t>
+          <t>3233077</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3289503</t>
+          <t>3288383</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3185861</t>
+          <t>3190205</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3258248</t>
+          <t>3256210</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6444691</t>
+          <t>6441902</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6530944</t>
+          <t>6535879</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26216</t>
+          <t>25072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19221</t>
+          <t>19261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40639</t>
+          <t>40689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33209</t>
+          <t>33213</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59988</t>
+          <t>60153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267545</t>
+          <t>268689</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284366</t>
+          <t>284249</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248064</t>
+          <t>248014</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269482</t>
+          <t>269442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>522476</t>
+          <t>522311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>549255</t>
+          <t>549251</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20296</t>
+          <t>21640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29705</t>
+          <t>29527</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20943</t>
+          <t>20925</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>43554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>482279</t>
+          <t>480935</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496517</t>
+          <t>496339</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>493379</t>
+          <t>493557</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511674</t>
+          <t>511727</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>982640</t>
+          <t>982105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1004716</t>
+          <t>1004734</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308258</t>
+          <t>308439</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316991</t>
+          <t>316916</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328442</t>
+          <t>328708</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640828</t>
+          <t>640841</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651143</t>
+          <t>651019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26315</t>
+          <t>26082</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17666</t>
+          <t>18914</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38865</t>
+          <t>40305</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32463</t>
+          <t>32561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58537</t>
+          <t>58499</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342676</t>
+          <t>342909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358989</t>
+          <t>359176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348418</t>
+          <t>346978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369617</t>
+          <t>368369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>697737</t>
+          <t>697775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>723811</t>
+          <t>723713</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25090</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15498</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35078</t>
+          <t>33748</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197058</t>
+          <t>197190</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207330</t>
+          <t>208177</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>191977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208599</t>
+          <t>208475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>393843</t>
+          <t>395173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>413051</t>
+          <t>413423</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>13017</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32173</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46884</t>
+          <t>44978</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245303</t>
+          <t>244712</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257750</t>
+          <t>257910</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>240942</t>
+          <t>239786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259530</t>
+          <t>260098</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>489354</t>
+          <t>491260</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>513781</t>
+          <t>513987</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39389</t>
+          <t>40220</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37667</t>
+          <t>38183</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66956</t>
+          <t>68358</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62756</t>
+          <t>61581</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97296</t>
+          <t>95574</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>617169</t>
+          <t>616338</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638893</t>
+          <t>638825</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>623067</t>
+          <t>621665</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>652356</t>
+          <t>651840</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1249285</t>
+          <t>1251007</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1283825</t>
+          <t>1285000</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33792</t>
+          <t>34635</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43966</t>
+          <t>43588</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38305</t>
+          <t>38057</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68130</t>
+          <t>68458</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>744791</t>
+          <t>743948</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>764711</t>
+          <t>764853</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>780166</t>
+          <t>780544</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>804759</t>
+          <t>804071</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1534585</t>
+          <t>1534257</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1564410</t>
+          <t>1564658</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>96531</t>
+          <t>96776</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>140779</t>
+          <t>141560</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>168680</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>226190</t>
+          <t>224144</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>279351</t>
+          <t>281018</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>353703</t>
+          <t>352040</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3252599</t>
+          <t>3251818</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3296847</t>
+          <t>3296602</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3313314</t>
+          <t>3315360</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3369504</t>
+          <t>3370824</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6579178</t>
+          <t>6580841</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6653530</t>
+          <t>6651863</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -10697,102 +10697,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3164</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6864</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>7280</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>3813</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>13687</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3219</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7146</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>7969</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>3980</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>14646</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -10810,102 +10810,102 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>306693</t>
+          <t>314729</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>299794</t>
+          <t>309975</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309561</t>
+          <t>317520</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>312897</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>309197</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>314688</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>627626</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>621219</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>631093</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>97,84%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>99,4%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>286416</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>282489</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>288606</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>593108</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>586431</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>597097</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21679</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34265</t>
+          <t>35697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39190</t>
+          <t>40665</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29787</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50228</t>
+          <t>51872</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>60868</t>
+          <t>62903</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46929</t>
+          <t>48841</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75919</t>
+          <t>78489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>495840</t>
+          <t>507420</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483254</t>
+          <t>493961</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504346</t>
+          <t>516201</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>475779</t>
+          <t>505829</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464741</t>
+          <t>494622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485182</t>
+          <t>516229</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>971620</t>
+          <t>1013249</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>956569</t>
+          <t>997663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>985559</t>
+          <t>1027311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517519</t>
+          <t>529658</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517519</t>
+          <t>529658</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517519</t>
+          <t>529658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032488</t>
+          <t>1076152</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032488</t>
+          <t>1076152</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032488</t>
+          <t>1076152</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23624</t>
+          <t>23149</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>16229</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33697</t>
+          <t>31758</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37538</t>
+          <t>38670</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29543</t>
+          <t>31051</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46991</t>
+          <t>48561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,17 +11453,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>61162</t>
+          <t>61819</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50117</t>
+          <t>50769</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75231</t>
+          <t>74409</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>291422</t>
+          <t>291910</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281349</t>
+          <t>283301</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>298218</t>
+          <t>298830</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>311590</t>
+          <t>317711</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>302137</t>
+          <t>307820</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319585</t>
+          <t>325330</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,17 +11566,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>603011</t>
+          <t>609622</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>588942</t>
+          <t>597032</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>614056</t>
+          <t>620672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315046</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315046</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315046</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664173</t>
+          <t>671441</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664173</t>
+          <t>671441</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664173</t>
+          <t>671441</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>34580</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25993</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15095</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36552</t>
+          <t>37010</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>45646</t>
+          <t>49339</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32341</t>
+          <t>38297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61047</t>
+          <t>64401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>292904</t>
+          <t>352261</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>282574</t>
+          <t>338565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300799</t>
+          <t>360303</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>446277</t>
+          <t>389816</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>435718</t>
+          <t>381261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>457175</t>
+          <t>396748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>739180</t>
+          <t>742077</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>723779</t>
+          <t>727015</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752485</t>
+          <t>753119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>472270</t>
+          <t>418271</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>472270</t>
+          <t>418271</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>472270</t>
+          <t>418271</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>784826</t>
+          <t>791416</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>784826</t>
+          <t>791416</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>784826</t>
+          <t>791416</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,102 +12069,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10765</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7097</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15487</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>18848</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>13668</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>25393</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>4,36%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>10237</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6945</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14636</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>18030</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>12920</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>24337</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -12182,102 +12182,102 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>170949</t>
+          <t>197582</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165474</t>
+          <t>192562</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173991</t>
+          <t>201095</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>96,07%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,63%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>216018</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>211296</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>219686</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>93,17%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>413600</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>407055</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>418780</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>95,64%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>198007</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>193608</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>201299</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,08%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>92,97%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>368956</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>362649</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>374066</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>95,34%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208244</t>
+          <t>226783</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208244</t>
+          <t>226783</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208244</t>
+          <t>226783</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386986</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386986</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386986</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14463</t>
+          <t>14380</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>21072</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>23102</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17815</t>
+          <t>17864</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29866</t>
+          <t>29844</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37363</t>
+          <t>37483</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29636</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45834</t>
+          <t>45683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>255173</t>
+          <t>256327</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249160</t>
+          <t>249635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260260</t>
+          <t>260637</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>234156</t>
+          <t>240648</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>227190</t>
+          <t>233906</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>239241</t>
+          <t>245886</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>489329</t>
+          <t>496974</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>480858</t>
+          <t>488774</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>497056</t>
+          <t>504487</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>41065</t>
+          <t>51349</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30435</t>
+          <t>37490</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55379</t>
+          <t>69878</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>58741</t>
+          <t>72435</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28067</t>
+          <t>59426</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82136</t>
+          <t>87454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>99805</t>
+          <t>123784</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65634</t>
+          <t>103303</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>123215</t>
+          <t>146670</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>582185</t>
+          <t>667256</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>567871</t>
+          <t>648727</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>592815</t>
+          <t>681115</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>790524</t>
+          <t>699622</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>767129</t>
+          <t>684603</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>821198</t>
+          <t>712631</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1372709</t>
+          <t>1366878</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1349299</t>
+          <t>1343992</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1406880</t>
+          <t>1387359</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>35055</t>
+          <t>40251</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>29230</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53874</t>
+          <t>53700</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>52258</t>
+          <t>60895</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42368</t>
+          <t>49280</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64239</t>
+          <t>74771</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>87313</t>
+          <t>101146</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54716</t>
+          <t>84834</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>110011</t>
+          <t>120422</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>893045</t>
+          <t>757153</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>874226</t>
+          <t>743704</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>911921</t>
+          <t>768174</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>664764</t>
+          <t>769656</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>652783</t>
+          <t>755780</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>674654</t>
+          <t>781271</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1557809</t>
+          <t>1526809</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1535111</t>
+          <t>1507533</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590406</t>
+          <t>1543121</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797404</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797404</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797404</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717022</t>
+          <t>830551</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717022</t>
+          <t>830551</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717022</t>
+          <t>830551</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1645122</t>
+          <t>1627955</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1645122</t>
+          <t>1627955</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1645122</t>
+          <t>1627955</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>168081</t>
+          <t>184452</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>130009</t>
+          <t>160618</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>196862</t>
+          <t>213718</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>250076</t>
+          <t>278150</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>203776</t>
+          <t>253214</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>280250</t>
+          <t>305625</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>418157</t>
+          <t>462601</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>361230</t>
+          <t>427953</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>459412</t>
+          <t>501471</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3288211</t>
+          <t>3344637</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3259430</t>
+          <t>3315371</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3326283</t>
+          <t>3368471</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3407511</t>
+          <t>3452198</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3377337</t>
+          <t>3424723</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3453811</t>
+          <t>3477134</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6695722</t>
+          <t>6796837</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6654467</t>
+          <t>6757967</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6752649</t>
+          <t>6831485</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3456292</t>
+          <t>3529089</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3456292</t>
+          <t>3529089</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3456292</t>
+          <t>3529089</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657587</t>
+          <t>3730348</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657587</t>
+          <t>3730348</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657587</t>
+          <t>3730348</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7113879</t>
+          <t>7259438</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7113879</t>
+          <t>7259438</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7113879</t>
+          <t>7259438</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
